--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484833_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484833_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.8918</v>
+        <v>9.3202</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0554</v>
+        <v>6.8807</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8364</v>
+        <v>2.4396</v>
       </c>
       <c r="G2" t="n">
         <v>5.4507</v>
@@ -610,13 +610,13 @@
         <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9505</v>
+        <v>1.379</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.4901</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2857</v>
+        <v>0.8889</v>
       </c>
       <c r="V2" t="n">
         <v>0.6036</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.7404</v>
+        <v>7.9646</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7497</v>
+        <v>4.8416</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9908</v>
+        <v>3.123</v>
       </c>
       <c r="G3" t="n">
         <v>4.1573</v>
@@ -688,13 +688,13 @@
         <v>2.4531</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1716</v>
+        <v>1.0525</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7642</v>
+        <v>0.3277</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5926</v>
+        <v>0.7249</v>
       </c>
       <c r="V3" t="n">
         <v>1.2452</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.0313</v>
+        <v>6.7481</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7207</v>
+        <v>6.3053</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3106</v>
+        <v>0.4429</v>
       </c>
       <c r="G4" t="n">
         <v>3.7427</v>
@@ -766,13 +766,13 @@
         <v>1.887</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.221</v>
+        <v>0.4959</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4703</v>
+        <v>0.1143</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2493</v>
+        <v>0.3816</v>
       </c>
       <c r="V4" t="n">
         <v>0.6226</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.5715</v>
+        <v>5.5533</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1136</v>
+        <v>4.9951</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4579</v>
+        <v>0.5582</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2567</v>
+        <v>3.5826</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0402</v>
+        <v>3.0584</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7835</v>
+        <v>0.5242</v>
       </c>
       <c r="J5" t="n">
-        <v>1.62</v>
+        <v>4.19</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5378</v>
+        <v>3.4497</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0823</v>
+        <v>0.7403</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3633</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5024</v>
+        <v>-0.3913</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8657</v>
+        <v>-0.2162</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1887</v>
+        <v>0.7548</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0757</v>
+        <v>1.6983</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1261</v>
+        <v>0.5933</v>
       </c>
       <c r="T5" t="n">
-        <v>3.3806</v>
+        <v>-0.1192</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7454</v>
+        <v>0.7125</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.8678</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.3257</v>
+        <v>4.8831</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6253</v>
+        <v>4.2356</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7004</v>
+        <v>0.6475</v>
       </c>
       <c r="G6" t="n">
         <v>3.8342</v>
@@ -922,13 +922,13 @@
         <v>1.5096</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5672</v>
+        <v>1.1246</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9464</v>
+        <v>0.5567</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6208</v>
+        <v>0.5679</v>
       </c>
       <c r="V6" t="n">
         <v>1.2452</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>H. MARTORELL TRONCHONI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>5.2815</v>
+        <v>4.6855</v>
       </c>
       <c r="E7" t="n">
-        <v>4.644</v>
+        <v>1.4347</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6375</v>
+        <v>3.2508</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5826</v>
+        <v>2.4048</v>
       </c>
       <c r="H7" t="n">
-        <v>3.0584</v>
+        <v>1.3289</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5242</v>
+        <v>1.0759</v>
       </c>
       <c r="J7" t="n">
-        <v>4.19</v>
+        <v>1.2415</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4497</v>
+        <v>0.5337</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7403</v>
+        <v>0.7077</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6074000000000001</v>
+        <v>1.1633</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3913</v>
+        <v>0.7951</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2162</v>
+        <v>0.3682</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7548</v>
+        <v>1.6983</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>1.6983</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3216</v>
+        <v>0.5824</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4703</v>
+        <v>0.1932</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7919</v>
+        <v>0.3892</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8678</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. MARTORELL TRONCHONI</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4.119</v>
+        <v>3.6022</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9475</v>
+        <v>1.2238</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1714</v>
+        <v>2.3785</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4048</v>
+        <v>1.2567</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3289</v>
+        <v>2.0402</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0759</v>
+        <v>-0.7835</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2415</v>
+        <v>1.62</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5337</v>
+        <v>1.5378</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7077</v>
+        <v>0.0823</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1633</v>
+        <v>-0.3633</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7951</v>
+        <v>0.5024</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3682</v>
+        <v>-0.8657</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6983</v>
+        <v>0.1887</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6983</v>
+        <v>2.0757</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0159</v>
+        <v>2.1568</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2939</v>
+        <v>1.4907</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3098</v>
+        <v>0.6661</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6695</v>
+        <v>1.5922</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8704</v>
+        <v>-0.9477</v>
       </c>
       <c r="F9" t="n">
         <v>2.5399</v>
@@ -1156,10 +1156,10 @@
         <v>1.887</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6518</v>
+        <v>1.5746</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7236</v>
+        <v>0.6463</v>
       </c>
       <c r="U9" t="n">
         <v>0.9283</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0979</v>
+        <v>0.885</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4361</v>
+        <v>1.1438</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3382</v>
+        <v>-0.2588</v>
       </c>
       <c r="G10" t="n">
         <v>0.9863</v>
@@ -1234,13 +1234,13 @@
         <v>0.3774</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6778</v>
+        <v>0.4649</v>
       </c>
       <c r="T10" t="n">
-        <v>0.532</v>
+        <v>0.2397</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1458</v>
+        <v>0.2252</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5506</v>
+        <v>-1.1608</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7121</v>
+        <v>-1.3224</v>
       </c>
       <c r="F11" t="n">
         <v>0.1616</v>
@@ -1312,10 +1312,10 @@
         <v>1.3209</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3034</v>
+        <v>0.6931</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2816</v>
+        <v>0.1081</v>
       </c>
       <c r="U11" t="n">
         <v>0.585</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. MALLIK BOUNAD</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4728</v>
+        <v>-3.9147</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5717</v>
+        <v>-4.2026</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9011</v>
+        <v>0.2879</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5615</v>
+        <v>-2.1142</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0183</v>
+        <v>1.1442</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5432</v>
+        <v>-3.2583</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0991</v>
+        <v>-0.614</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1403</v>
+        <v>1.1942</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0411</v>
+        <v>-1.8083</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4624</v>
+        <v>-1.5001</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8781</v>
+        <v>-0.0501</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5843</v>
+        <v>-1.4501</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3209</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.887</v>
+        <v>-3.774</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5661</v>
+        <v>1.5096</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6549</v>
+        <v>0.7657</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4144</v>
+        <v>0.1854</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2404</v>
+        <v>0.5803</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>R. MALLIK BOUNAD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.7756</v>
+        <v>-4.6412</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9048</v>
+        <v>-2.7666</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1292</v>
+        <v>-1.8746</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.1142</v>
+        <v>-2.5615</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1442</v>
+        <v>-2.0183</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.2583</v>
+        <v>-0.5432</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.614</v>
+        <v>-1.0991</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1942</v>
+        <v>-1.1403</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.8083</v>
+        <v>0.0411</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5001</v>
+        <v>-1.4624</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0501</v>
+        <v>-0.8781</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.4501</v>
+        <v>-0.5843</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.2644</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.774</v>
+        <v>-1.887</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.4864</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5168</v>
+        <v>0.2195</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4215</v>
+        <v>0.2669</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>34.92960000000001</v>
+        <v>35.5175</v>
       </c>
       <c r="E14" t="n">
-        <v>21.2333</v>
+        <v>21.8213</v>
       </c>
       <c r="F14" t="n">
-        <v>13.6964</v>
+        <v>13.6965</v>
       </c>
       <c r="G14" t="n">
         <v>22.9415</v>
@@ -1516,7 +1516,7 @@
         <v>20.559</v>
       </c>
       <c r="I14" t="n">
-        <v>2.382700000000001</v>
+        <v>2.3827</v>
       </c>
       <c r="J14" t="n">
         <v>31.9376</v>
@@ -1537,7 +1537,7 @@
         <v>-8.331099999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.886999999999999</v>
+        <v>-1.887</v>
       </c>
       <c r="Q14" t="n">
         <v>-20.757</v>
@@ -1546,13 +1546,13 @@
         <v>18.87</v>
       </c>
       <c r="S14" t="n">
-        <v>10.7814</v>
+        <v>11.3692</v>
       </c>
       <c r="T14" t="n">
-        <v>3.864699999999999</v>
+        <v>4.452500000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>6.916500000000001</v>
+        <v>6.916799999999999</v>
       </c>
       <c r="V14" t="n">
         <v>3.094</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7166</v>
+        <v>0.9885</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1441</v>
+        <v>3.3389</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4274</v>
+        <v>-2.3504</v>
       </c>
       <c r="G16" t="n">
         <v>2.9575</v>
@@ -1702,13 +1702,13 @@
         <v>2.8305</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.0522</v>
+        <v>-1.7803</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3274</v>
+        <v>-1.1326</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7247</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.659</v>
+        <v>-0.3259</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1406</v>
+        <v>1.238</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7996</v>
+        <v>-1.5639</v>
       </c>
       <c r="G17" t="n">
         <v>1.3756</v>
@@ -1780,13 +1780,13 @@
         <v>1.3209</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9782</v>
+        <v>-0.645</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.458</v>
+        <v>-0.3605</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5202</v>
+        <v>-0.2845</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2452</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5922</v>
+        <v>-1.4683</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2041</v>
+        <v>-1.1067</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3881</v>
+        <v>-0.3616</v>
       </c>
       <c r="G18" t="n">
         <v>-2.5192</v>
@@ -1858,13 +1858,13 @@
         <v>1.1322</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2052</v>
+        <v>-0.0813</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0929</v>
+        <v>0.0045</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8284</v>
+        <v>-2.6275</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3463</v>
+        <v>-0.2488</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4821</v>
+        <v>-2.3786</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4943</v>
@@ -1936,13 +1936,13 @@
         <v>0.3774</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0323</v>
+        <v>-0.8314</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8107</v>
+        <v>-0.7133</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2216</v>
+        <v>-0.1181</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3018</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8638</v>
+        <v>-3.3706</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6555</v>
+        <v>2.0453</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.5193</v>
+        <v>-5.4158</v>
       </c>
       <c r="G20" t="n">
         <v>-4.386</v>
@@ -2014,13 +2014,13 @@
         <v>3.0192</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4779</v>
+        <v>-0.9847</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1387</v>
+        <v>-0.749</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3391</v>
+        <v>-0.2357</v>
       </c>
       <c r="V20" t="n">
         <v>0.3018</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.513</v>
+        <v>-4.4504</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3763</v>
+        <v>-4.1814</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1368</v>
+        <v>-0.269</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4689</v>
@@ -2092,13 +2092,13 @@
         <v>2.0757</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4214</v>
+        <v>-1.3588</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9747</v>
+        <v>-0.7798</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4467</v>
+        <v>-0.579</v>
       </c>
       <c r="V21" t="n">
         <v>0.3208</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.6364</v>
+        <v>-6.4171</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1498</v>
+        <v>-2.2215</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.4866</v>
+        <v>-4.1956</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2678</v>
@@ -2170,13 +2170,13 @@
         <v>3.774</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6138</v>
+        <v>-1.3946</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2097</v>
+        <v>-0.862</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8235</v>
+        <v>-0.5325</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2452</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.644399999999999</v>
+        <v>-8.8765</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.1825</v>
+        <v>-6.2799</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4619</v>
+        <v>-2.5966</v>
       </c>
       <c r="G23" t="n">
         <v>-9.3551</v>
@@ -2248,13 +2248,13 @@
         <v>3.774</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9312</v>
+        <v>-1.1632</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8542</v>
+        <v>-0.9517</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0769</v>
+        <v>-0.2116</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6226</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.1431</v>
+        <v>-8.9663</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.6116</v>
+        <v>-7.5141</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5315</v>
+        <v>-1.4521</v>
       </c>
       <c r="G24" t="n">
         <v>-6.0172</v>
@@ -2326,13 +2326,13 @@
         <v>2.4531</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.0692</v>
+        <v>-1.8924</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.4697</v>
+        <v>-1.3723</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5995</v>
+        <v>-0.5202</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3018</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-34.9298</v>
+        <v>-34.2802</v>
       </c>
       <c r="E25" t="n">
-        <v>-13.6965</v>
+        <v>-13.6963</v>
       </c>
       <c r="F25" t="n">
-        <v>-21.2333</v>
+        <v>-20.5836</v>
       </c>
       <c r="G25" t="n">
         <v>-22.9415</v>
@@ -2404,13 +2404,13 @@
         <v>20.757</v>
       </c>
       <c r="S25" t="n">
-        <v>-10.7814</v>
+        <v>-10.1317</v>
       </c>
       <c r="T25" t="n">
-        <v>-6.916599999999999</v>
+        <v>-6.9167</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.8645</v>
+        <v>-3.2151</v>
       </c>
       <c r="V25" t="n">
         <v>-3.094</v>
